--- a/data/trans_camb/P32B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,69</t>
+          <t>0,41; 4,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,45</t>
+          <t>0,03; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 6,31</t>
+          <t>0,1; 5,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,0</t>
+          <t>-4,09; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,21</t>
+          <t>-3,04; 1,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,13</t>
+          <t>-1,91; 2,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,96</t>
+          <t>-0,11; 2,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,9</t>
+          <t>-0,27; 2,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,84</t>
+          <t>0,11; 3,9</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,54; —</t>
+          <t>-28,09; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,34; —</t>
+          <t>-59,39; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,03; —</t>
+          <t>-83,57; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 1459,52</t>
+          <t>-51,17; 1334,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,62; —</t>
+          <t>-59,85; 1304,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,86; —</t>
+          <t>-28,12; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,8</t>
+          <t>-1,32; 0,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,3</t>
+          <t>-0,41; 3,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,95</t>
+          <t>-1,35; 0,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,74</t>
+          <t>-2,04; 3,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,06</t>
+          <t>-3,42; 0,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,56</t>
+          <t>-1,88; 3,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,3</t>
+          <t>-1,41; 1,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,64</t>
+          <t>-1,1; 1,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,6</t>
+          <t>-1,0; 1,49</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,42; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,58; 672,23</t>
+          <t>-80,63; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,31; —</t>
+          <t>-71,8; 611,17</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,51</t>
+          <t>1,59; 6,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,21</t>
+          <t>0,05; 3,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,34</t>
+          <t>-0,06; 4,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,47</t>
+          <t>0,0; 12,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,2</t>
+          <t>1,3; 5,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,53</t>
+          <t>0,34; 3,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,52</t>
+          <t>-0,09; 3,62</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,55; —</t>
+          <t>40,44; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,82; —</t>
+          <t>-55,8; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,75; —</t>
+          <t>41,64; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,7; —</t>
+          <t>-31,61; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-96,48; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,02</t>
+          <t>0,43; 3,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,66</t>
+          <t>-0,53; 2,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,94</t>
+          <t>-0,55; 3,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,36</t>
+          <t>-4,02; 0,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,68</t>
+          <t>-2,81; 1,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,48</t>
+          <t>-4,19; 0,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,81</t>
+          <t>-0,22; 2,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,91</t>
+          <t>-0,6; 1,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,4</t>
+          <t>-1,32; 1,45</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 602,53</t>
+          <t>3,44; 630,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 384,63</t>
+          <t>-32,61; 395,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 422,36</t>
+          <t>-40,51; 416,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 152,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 331,59</t>
+          <t>-17,2; 290,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 235,29</t>
+          <t>-36,07; 211,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 173,05</t>
+          <t>-65,72; 171,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,75</t>
+          <t>-0,37; 2,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,4</t>
+          <t>-0,01; 3,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,17</t>
+          <t>0,76; 5,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,82</t>
+          <t>-3,38; 1,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,0</t>
+          <t>-5,53; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,11</t>
+          <t>-2,94; 2,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,84</t>
+          <t>-1,0; 1,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,58</t>
+          <t>-1,21; 1,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,48</t>
+          <t>0,25; 3,88</t>
         </is>
       </c>
     </row>
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,36; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-66,9; —</t>
+          <t>-68,73; 721,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,91; 769,09</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 1114,63</t>
+          <t>-14,73; —</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,67; 8,57</t>
+          <t>0,98; 9,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,21</t>
+          <t>-0,75; 4,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 0,0</t>
+          <t>-4,33; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,77</t>
+          <t>-1,04; 1,47</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,76</t>
+          <t>-0,52; 3,02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 8,85</t>
+          <t>-0,92; 9,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,36</t>
+          <t>0,01; 3,41</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,83</t>
+          <t>-0,12; 2,87</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,5</t>
+          <t>-0,87; 4,13</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-28,72; —</t>
+          <t>-38,7; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-41,57; —</t>
+          <t>-50,29; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,94</t>
+          <t>1,18; 2,98</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,12</t>
+          <t>0,48; 2,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,06</t>
+          <t>0,36; 2,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,37</t>
+          <t>-1,22; 0,48</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,88</t>
+          <t>-0,98; 0,79</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,19</t>
+          <t>-0,99; 1,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,9</t>
+          <t>0,57; 1,86</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,42</t>
+          <t>0,23; 1,43</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,51</t>
+          <t>0,14; 1,58</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>92,7; 534,12</t>
+          <t>84,93; 582,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>37,22; 397,11</t>
+          <t>35,11; 401,06</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22,15; 388,76</t>
+          <t>20,43; 375,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-80,22; 86,74</t>
+          <t>-81,4; 97,0</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-61,63; 165,1</t>
+          <t>-64,69; 148,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,79; 210,12</t>
+          <t>-60,08; 204,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>51,46; 294,19</t>
+          <t>44,34; 266,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>18,84; 226,39</t>
+          <t>16,04; 216,89</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,06; 221,73</t>
+          <t>8,92; 231,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32B-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,63</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,71</t>
+          <t>0,36; 4,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,51</t>
+          <t>0,02; 4,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 5,61</t>
+          <t>0,25; 5,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,0</t>
+          <t>-4,69; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,22</t>
+          <t>-3,08; 1,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,28</t>
+          <t>-2,32; 2,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,94</t>
+          <t>-0,11; 3,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,87</t>
+          <t>-0,3; 2,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,9</t>
+          <t>0,22; 3,99</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>298,95%</t>
+          <t>358,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>202,96%</t>
+          <t>235,79%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,09; —</t>
+          <t>-46,28; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,39; —</t>
+          <t>-62,8; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,57; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,17; 1334,99</t>
+          <t>-39,67; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,85; 1304,3</t>
+          <t>-60,43; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,12; —</t>
+          <t>-35,71; 1802,93</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,79</t>
+          <t>-1,49; 0,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,56</t>
+          <t>-0,44; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,83</t>
+          <t>-1,01; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,22</t>
+          <t>-2,05; 3,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,94</t>
+          <t>-4,12; 0,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 3,68</t>
+          <t>-1,66; 4,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,25</t>
+          <t>-1,35; 1,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,73</t>
+          <t>-1,0; 1,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,49</t>
+          <t>-0,67; 2,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-3,59%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>113,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,63; —</t>
+          <t>-85,09; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,8; 611,17</t>
+          <t>-63,68; —</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,84</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,2</t>
+          <t>1,49; 6,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,14</t>
+          <t>-0,12; 3,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,08</t>
+          <t>0,19; 6,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,16</t>
+          <t>0,0; 11,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,0</t>
+          <t>1,16; 5,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,81</t>
+          <t>0,3; 3,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,62</t>
+          <t>0,29; 5,05</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>284,27%</t>
+          <t>433,71%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>281,52%</t>
+          <t>424,05%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,44; —</t>
+          <t>19,93; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,8; —</t>
+          <t>-71,81; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,64; —</t>
+          <t>40,98; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,61; —</t>
+          <t>-24,69; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-96,48; —</t>
+          <t>-40,86; —</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,84</t>
+          <t>0,26; 3,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,72</t>
+          <t>-0,5; 2,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,06</t>
+          <t>-0,72; 2,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,32</t>
+          <t>-3,99; 0,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,62</t>
+          <t>-2,89; 1,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,45</t>
+          <t>-2,11; 3,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,61</t>
+          <t>-0,03; 2,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,79</t>
+          <t>-0,63; 1,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,45</t>
+          <t>-0,71; 1,95</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-69,41%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 630,52</t>
+          <t>2,41; 602,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 395,61</t>
+          <t>-34,23; 430,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 416,1</t>
+          <t>-48,96; 315,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,26; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 152,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 290,02</t>
+          <t>-11,17; 324,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 211,02</t>
+          <t>-36,44; 216,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 171,62</t>
+          <t>-47,73; 206,73</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,74</t>
+          <t>-0,27; 2,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,47</t>
+          <t>-0,15; 3,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,28</t>
+          <t>0,88; 5,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,76</t>
+          <t>-3,6; 1,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,0</t>
+          <t>-5,31; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,97</t>
+          <t>-2,74; 2,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,76</t>
+          <t>-0,93; 1,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,65</t>
+          <t>-1,13; 1,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,88</t>
+          <t>0,23; 3,73</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>591,2%</t>
+          <t>658,4%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>201,32%</t>
+          <t>212,02%</t>
         </is>
       </c>
     </row>
@@ -1672,29 +1672,29 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,36; —</t>
+          <t>-88,47; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,73; 721,62</t>
+          <t>-69,77; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-77,91; 769,09</t>
+          <t>-77,34; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,73; —</t>
+          <t>-12,52; 1513,4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,47</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,24</t>
+          <t>1,12; 8,65</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,8</t>
+          <t>-1,12; 4,39</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,0</t>
+          <t>-3,74; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,47</t>
+          <t>-1,11; 1,47</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,02</t>
+          <t>-0,53; 2,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,04</t>
+          <t>-0,93; 8,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,41</t>
+          <t>0,14; 3,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,87</t>
+          <t>-0,1; 2,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,13</t>
+          <t>-0,88; 4,91</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>293,24%</t>
+          <t>276,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-38,7; —</t>
+          <t>-31,45; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-50,29; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>1,13</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,98</t>
+          <t>1,19; 3,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,11</t>
+          <t>0,57; 2,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,28</t>
+          <t>0,52; 2,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,48</t>
+          <t>-1,36; 0,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,79</t>
+          <t>-0,91; 0,81</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,22</t>
+          <t>-0,24; 1,97</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,86</t>
+          <t>0,57; 1,9</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,43</t>
+          <t>0,24; 1,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,58</t>
+          <t>0,53; 1,95</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>144,17%</t>
+          <t>164,45%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>127,29%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>84,93; 582,65</t>
+          <t>86,06; 547,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>35,11; 401,06</t>
+          <t>31,96; 375,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20,43; 375,01</t>
+          <t>29,09; 365,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-81,4; 97,0</t>
+          <t>-79,28; 87,59</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-64,69; 148,95</t>
+          <t>-58,57; 156,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,08; 204,15</t>
+          <t>-22,15; 379,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>44,34; 266,79</t>
+          <t>49,21; 293,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>16,04; 216,89</t>
+          <t>18,24; 226,58</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8,92; 231,09</t>
+          <t>46,29; 296,0</t>
         </is>
       </c>
     </row>
